--- a/misdata/FINBOX_Standardized_MIS_Template.xlsx
+++ b/misdata/FINBOX_Standardized_MIS_Template.xlsx
@@ -19,9 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -666,217 +664,217 @@
         </is>
       </c>
       <c r="B1" s="5" t="n">
-        <v>43951</v>
+        <v>43922.5</v>
       </c>
       <c r="C1" s="5" t="n">
-        <v>43982</v>
+        <v>43952.5</v>
       </c>
       <c r="D1" s="5" t="n">
-        <v>44012</v>
+        <v>43983.5</v>
       </c>
       <c r="E1" s="5" t="n">
-        <v>44043</v>
+        <v>44013.5</v>
       </c>
       <c r="F1" s="5" t="n">
-        <v>44074</v>
+        <v>44044.5</v>
       </c>
       <c r="G1" s="5" t="n">
-        <v>44104</v>
+        <v>44075.5</v>
       </c>
       <c r="H1" s="5" t="n">
-        <v>44135</v>
+        <v>44105.5</v>
       </c>
       <c r="I1" s="5" t="n">
-        <v>44165</v>
+        <v>44136.5</v>
       </c>
       <c r="J1" s="5" t="n">
-        <v>44196</v>
+        <v>44166.5</v>
       </c>
       <c r="K1" s="5" t="n">
-        <v>44227</v>
+        <v>44197.5</v>
       </c>
       <c r="L1" s="5" t="n">
-        <v>44255</v>
+        <v>44228.5</v>
       </c>
       <c r="M1" s="5" t="n">
-        <v>44286</v>
+        <v>44256.5</v>
       </c>
       <c r="N1" s="5" t="n">
-        <v>44316</v>
+        <v>44287.5</v>
       </c>
       <c r="O1" s="5" t="n">
-        <v>44347</v>
+        <v>44317.5</v>
       </c>
       <c r="P1" s="5" t="n">
-        <v>44377</v>
+        <v>44348.5</v>
       </c>
       <c r="Q1" s="5" t="n">
-        <v>44408</v>
+        <v>44378.5</v>
       </c>
       <c r="R1" s="5" t="n">
-        <v>44439</v>
+        <v>44409.5</v>
       </c>
       <c r="S1" s="5" t="n">
-        <v>44469</v>
+        <v>44440.5</v>
       </c>
       <c r="T1" s="5" t="n">
-        <v>44500</v>
+        <v>44470.5</v>
       </c>
       <c r="U1" s="5" t="n">
-        <v>44530</v>
+        <v>44501.5</v>
       </c>
       <c r="V1" s="5" t="n">
-        <v>44561</v>
+        <v>44531.5</v>
       </c>
       <c r="W1" s="5" t="n">
-        <v>44592</v>
+        <v>44562.5</v>
       </c>
       <c r="X1" s="5" t="n">
-        <v>44620</v>
+        <v>44593.5</v>
       </c>
       <c r="Y1" s="5" t="n">
-        <v>44651</v>
+        <v>44621.5</v>
       </c>
       <c r="Z1" s="5" t="n">
-        <v>44681</v>
+        <v>44652.5</v>
       </c>
       <c r="AA1" s="5" t="n">
-        <v>44712</v>
+        <v>44682.5</v>
       </c>
       <c r="AB1" s="5" t="n">
-        <v>44742</v>
+        <v>44713.5</v>
       </c>
       <c r="AC1" s="5" t="n">
-        <v>44773</v>
+        <v>44743.5</v>
       </c>
       <c r="AD1" s="5" t="n">
-        <v>44804</v>
+        <v>44774.5</v>
       </c>
       <c r="AE1" s="5" t="n">
-        <v>44834</v>
+        <v>44805.5</v>
       </c>
       <c r="AF1" s="5" t="n">
-        <v>44865</v>
+        <v>44835.5</v>
       </c>
       <c r="AG1" s="5" t="n">
-        <v>44895</v>
+        <v>44866.5</v>
       </c>
       <c r="AH1" s="5" t="n">
-        <v>44926</v>
+        <v>44896.5</v>
       </c>
       <c r="AI1" s="5" t="n">
-        <v>44957</v>
+        <v>44927.5</v>
       </c>
       <c r="AJ1" s="5" t="n">
-        <v>44985</v>
+        <v>44958.5</v>
       </c>
       <c r="AK1" s="5" t="n">
-        <v>45016</v>
+        <v>44986.5</v>
       </c>
       <c r="AL1" s="5" t="n">
-        <v>45017</v>
+        <v>45017.5</v>
       </c>
       <c r="AM1" s="5" t="n">
-        <v>45047</v>
+        <v>45047.5</v>
       </c>
       <c r="AN1" s="5" t="n">
-        <v>45078</v>
+        <v>45078.5</v>
       </c>
       <c r="AO1" s="5" t="n">
-        <v>45108</v>
+        <v>45108.5</v>
       </c>
       <c r="AP1" s="5" t="n">
-        <v>45139</v>
+        <v>45139.5</v>
       </c>
       <c r="AQ1" s="5" t="n">
-        <v>45170</v>
+        <v>45170.5</v>
       </c>
       <c r="AR1" s="5" t="n">
-        <v>45200</v>
+        <v>45200.5</v>
       </c>
       <c r="AS1" s="5" t="n">
-        <v>45231</v>
+        <v>45231.5</v>
       </c>
       <c r="AT1" s="5" t="n">
-        <v>45261</v>
+        <v>45261.5</v>
       </c>
       <c r="AU1" s="5" t="n">
-        <v>45292</v>
+        <v>45292.5</v>
       </c>
       <c r="AV1" s="5" t="n">
-        <v>45323</v>
+        <v>45323.5</v>
       </c>
       <c r="AW1" s="5" t="n">
-        <v>45352</v>
+        <v>45352.5</v>
       </c>
       <c r="AX1" s="5" t="n">
-        <v>45383</v>
+        <v>45383.5</v>
       </c>
       <c r="AY1" s="5" t="n">
-        <v>45413</v>
+        <v>45413.5</v>
       </c>
       <c r="AZ1" s="5" t="n">
-        <v>45444</v>
+        <v>45444.5</v>
       </c>
       <c r="BA1" s="5" t="n">
-        <v>45474</v>
+        <v>45474.5</v>
       </c>
       <c r="BB1" s="5" t="n">
-        <v>45505</v>
+        <v>45505.5</v>
       </c>
       <c r="BC1" s="5" t="n">
-        <v>45536</v>
+        <v>45536.5</v>
       </c>
       <c r="BD1" s="5" t="n">
-        <v>45566</v>
+        <v>45566.5</v>
       </c>
       <c r="BE1" s="5" t="n">
-        <v>45597</v>
+        <v>45597.5</v>
       </c>
       <c r="BF1" s="5" t="n">
-        <v>45627</v>
+        <v>45627.5</v>
       </c>
       <c r="BG1" s="5" t="n">
-        <v>45688</v>
+        <v>45658.5</v>
       </c>
       <c r="BH1" s="5" t="n">
-        <v>45716</v>
+        <v>45689.5</v>
       </c>
       <c r="BI1" s="5" t="n">
-        <v>45747</v>
+        <v>45717.5</v>
       </c>
       <c r="BJ1" s="5" t="n">
-        <v>45777</v>
+        <v>45748.5</v>
       </c>
       <c r="BK1" s="5" t="n">
-        <v>45808</v>
+        <v>45778.5</v>
       </c>
       <c r="BL1" s="5" t="n">
-        <v>45838</v>
+        <v>45809.5</v>
       </c>
       <c r="BM1" s="5" t="n">
-        <v>45869</v>
+        <v>45839.5</v>
       </c>
       <c r="BN1" s="5" t="n">
-        <v>45900</v>
+        <v>45870.5</v>
       </c>
       <c r="BO1" s="5" t="n">
-        <v>45930</v>
+        <v>45901.5</v>
       </c>
       <c r="BP1" s="5" t="n">
-        <v>45961</v>
+        <v>45931.5</v>
       </c>
       <c r="BQ1" s="5" t="n">
-        <v>45991</v>
+        <v>45962.5</v>
       </c>
       <c r="BR1" s="5" t="n">
-        <v>46022</v>
+        <v>45992.5</v>
       </c>
       <c r="BS1" s="5" t="n">
-        <v>46053</v>
+        <v>46023.5</v>
       </c>
       <c r="BT1" s="5" t="n">
-        <v>46081</v>
+        <v>46054.5</v>
       </c>
     </row>
     <row r="2">
